--- a/画面設計/【画面設計】03_料理検索結果.xlsx
+++ b/画面設計/【画面設計】03_料理検索結果.xlsx
@@ -321,7 +321,7 @@
       <rPr>
         <rFont val="Arial"/>
         <color theme="1"/>
-        <sz val="9.0"/>
+        <sz val="11.0"/>
       </rPr>
       <t>⭐︎</t>
     </r>
@@ -332,15 +332,7 @@
         <sz val="9.0"/>
       </rPr>
       <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="9.0"/>
-      </rPr>
-      <t>（★を表示しない場合）</t>
+（★を表示しない場合）</t>
     </r>
   </si>
   <si>
@@ -1154,6 +1146,48 @@
           </a:ln>
         </xdr:spPr>
       </xdr:pic>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="9" name="Shape 9"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3157875" y="4796325"/>
+            <a:ext cx="2587800" cy="410400"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="1400"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
@@ -1213,7 +1247,7 @@
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="9" name="Shape 9"/>
+          <xdr:cNvPr id="10" name="Shape 10"/>
           <xdr:cNvPicPr preferRelativeResize="0"/>
         </xdr:nvPicPr>
         <xdr:blipFill>
@@ -1240,7 +1274,7 @@
       </xdr:pic>
       <xdr:sp>
         <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="Shape 10"/>
+          <xdr:cNvPr id="11" name="Shape 11"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1286,7 +1320,7 @@
       </xdr:sp>
       <xdr:sp>
         <xdr:nvSpPr>
-          <xdr:cNvPr id="11" name="Shape 11"/>
+          <xdr:cNvPr id="12" name="Shape 12"/>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -1335,7 +1369,7 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="12" name="Shape 12"/>
+          <xdr:cNvPr id="13" name="Shape 13"/>
           <xdr:cNvPicPr preferRelativeResize="0"/>
         </xdr:nvPicPr>
         <xdr:blipFill>
@@ -1362,7 +1396,7 @@
       </xdr:pic>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="13" name="Shape 13"/>
+          <xdr:cNvPr id="14" name="Shape 14"/>
           <xdr:cNvPicPr preferRelativeResize="0"/>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
